--- a/data/ERGA_ODIKA_UNIFIED.xlsx
+++ b/data/ERGA_ODIKA_UNIFIED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mouhq-my.sharepoint.com/personal/ckourouklis_mou_gr/Documents/Qgis/1. Page combo Telika/roads_current/map-roads/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_A75A605B1059706FE76A745540DD1EB85657B408" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{219E706A-2F05-498A-A075-9CCF0A78BD99}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_A75A605B1059706FE76A745540DD1EB85657B408" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E05281A-01AB-409B-B241-7EB2F2C2D163}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ΒΑΣΗ ΕΡΓΩΝ" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="170">
   <si>
     <t>ΒΑΣΗ ΟΔΙΚΩΝ ΕΡΓΩΝ – ΕΔΥΜΕΤ</t>
   </si>
@@ -492,24 +492,6 @@
 Ειδικότερα αφορά στη μελέτη και κατασκευή των οδικών υποτμημάτων, από τον Μπράλο (χ.θ. 0+000) μέχρι την Αρχή παράκαμψης Γραβιάς (χ.θ. 7+300) και από τον Ισόπεδο Κόμβο Μεταλλείων Βωξίτη (χ.θ. 14+000) έως την Άμφισσα (χ.θ. 30+700), μήκους περίπου 24,0 km, με χαρακτηριστικά δίιχνης διατομής. Ενδιάμεσα έχει κατασκευαστεί η παράκαμψη της Γραβιάς και έχει υπογραφεί σύμβαση για την κατασκευή του οδικού τμήματος από Τέλος Παράκαμψης Γραβιάς έως χ.θ. 14+000, η οποία χρηματοδοτείται από το ΠεΠ ΣΤΕΡΕΑΣ ΕΛΛΑΔΑΣ 2021-2027. 
 Στην πράξη επίσης περιλαμβάνονται και όλες οι απαιτούμενες υποστηρικτικές δράσεις (απαλλοτριώσεις, μετατοπίσεις – αποκαταστάσεις δικτύων ΟΚΩ και συνδέσεις με αυτά, αρχαιολογικές έρευνες και εργασίες καθώς και Υπηρεσίες Συμβούλου για τον έλεγχο των μελετών του Αναδόχου κατασκευής του έργου).
 Στις 15.05.2026 εκδόθηκε η Απόφαση Τροποποίησης της πράξης προκειμένου να περιληφθεί μεταξύ άλλων η τροποποίηση του φυσικού αντικειμένου της πράξης που αφορά στην αντικατάσταση των σηράγγων αμφίδρομης κυκλοφορίας και των συνοδών σηράγγων διαφυγής με διαχωρισμένες σήραγγες μονής κατεύθυνσης με δυο λωρίδες κυκλοφορίας (η επιπλέον κατ' αποκοπή δαπάνη περιλαμβάνεται στην 1η ΣΣΕ που χρηματοδοτείται από το ΤΠΑ ΥΠΥΜΕ).   </t>
-  </si>
-  <si>
-    <t>"ΜεταφερόμενοέργοαποτοΕΠΥΜΕΠΕΡΑΑ2014-2020
-Κατασκευή σε πλήρη εξέλιξη με ανάδοχο την ΑΒΑΞ.
-Πρόοδος οικονομικής απορρόφησης: ~25,5% στην αρχική σύμβαση και ~9,7% στην 1η Σ.Σ.Ε. (15/05/2026).
-Συμβατική προθεσμία ολοκλήρωσης: 09/02/2028, βάσει της τελευταίας εγκεκριμένης παράτασης.
-1η Σ.Σ.Ε.: €69,25 εκατ. με ΦΠΑ, υπογεγραμμένη στις 12/12/2025 και χρηματοδοτούμενη από το ΤΠΑ/ΥΠΥΜΕ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"ΜεταφερόμενοέργοαποτοΕΠΥΜΕΠΕΡΑΑ2014-2020
-Ανάδοχος:""ΑΒΑΞΑ.Ε.""
-Ημερομηνίαυπογραφήςσύμβασης:15-2-2023
-Προθεσμίαπεραίωσηςεργασιών:31-12-2028,σύμφωναμετηντελευταίαεγκεκριμένηπαράταση(24-06-2026)
-Ποσόσύμβασης:
-ΑρχικήΣύμβαση:207.159.200,00€(χωρίςΦΠΑ)
-1ηΣ.Σ.Ε.:69.250.000,00€μεΦ.Π.Α.(ημερομηνίαυπογραφήςτης1ηςΣ.Σ.Ε.12.12.2025,μεχρηματοδότησηαπότοΤΠΑ/ΥΠΥΜΕ).
-Ποσοστόοικονομικήςαπορρόφησης:Α.Σ.:~29,5%(24οςΛογαριασμός/04.08.2026)και1ηςΣ.Σ.Ε.:~13%(8οςΛογαριασμος/04.08.2026)"
-</t>
   </si>
   <si>
     <t xml:space="preserve">Αρχική Σύμβαση: 207.159.200,00 € (χωρίς ΦΠΑ)
@@ -824,6 +806,26 @@
   </si>
   <si>
     <t xml:space="preserve"> 1η Σ.Σ.Ε.</t>
+  </si>
+  <si>
+    <t>"ΜεταφερόμενοέργοαποτοΕΠΥΜΕΠΕΡΑΑ2014-2020
+Κατασκευή σε πλήρη εξέλιξη με ανάδοχο την ΑΒΑΞ.
+Πρόοδος οικονομικής απορρόφησης:Ποσοστό οικονομικής απορρόφησης: Α.Σ.: ~29,5% (24ος Λογαριασμός/04.08.2026) και 1ης Σ.Σ.Ε.: ~13% (8ος Λογαριασμος/04.08.2026).
+Συμβατική προθεσμία ολοκλήρωσης: 09/02/2028, βάσει της τελευταίας εγκεκριμένης παράτασης.
+1η Σ.Σ.Ε.: €69,25 εκατ. με ΦΠΑ, υπογεγραμμένη στις 12/12/2025 και χρηματοδοτούμενη από το ΤΠΑ/ΥΠΥΜΕ.</t>
+  </si>
+  <si>
+    <t>Μεταφερόμενο έργο απο το ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020
+Ανάδοχος: "ΑΒΑΞ Α.Ε."
+Ημερομηνία υπογραφής σύμβασης: 15-2-2023
+Προθεσμία περαίωσης εργασιών:  31-12-2028, σύμφωνα με την τελευταία εγκεκριμένη παράταση (24-06-2026)
+Ποσό σύμβασης: 
+Αρχική Σύμβαση: 207.159.200,00 € (χωρίς ΦΠΑ)
+1η Σ.Σ.Ε.: 69.250.000,00 € με Φ.Π.Α. (ημερομηνία υπογραφής της 1ης Σ.Σ.Ε. 12.12.2025, με χρηματοδότηση από το ΤΠΑ/ΥΠΥΜΕ).
+Ποσοστό οικονομικής απορρόφησης: Α.Σ.: ~29,5% (24ος Λογαριασμός/04.08.2026) και 1ης Σ.Σ.Ε.: ~13% (8ος Λογαριασμος/04.08.2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Α.Σ </t>
   </si>
 </sst>
 </file>
@@ -1388,10 +1390,10 @@
       <c r="P4" s="5"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="T4" s="4"/>
       <c r="U4" s="4">
@@ -1450,10 +1452,10 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="T5" s="4"/>
       <c r="U5" s="4">
@@ -1510,10 +1512,10 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="T6" s="4"/>
       <c r="U6" s="4">
@@ -1572,13 +1574,13 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="T7" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="U7" s="4">
         <v>38.436501999999997</v>
@@ -1834,7 +1836,7 @@
         <v>101</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -1870,33 +1872,37 @@
         <v>104</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>104</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="K13" s="9">
         <v>262153306.08000001</v>
       </c>
       <c r="L13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="N13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="O13" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
+      <c r="R13" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>161</v>
+      </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4">
         <v>38.573256000000001</v>
@@ -1914,7 +1920,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E14" s="4">
         <v>6004817</v>
@@ -1923,34 +1929,34 @@
         <v>71</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="K14" s="9">
         <v>231080663.28999999</v>
       </c>
       <c r="L14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="O14" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="N14" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="P14" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -1970,38 +1976,38 @@
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="K15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="I15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="J15" s="7" t="s">
+      <c r="L15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="M15" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="N15" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="O15" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="4"/>
@@ -2024,23 +2030,23 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>131</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -2048,7 +2054,7 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -2069,49 +2075,49 @@
         <v>71</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="N17" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="O17" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="O17" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="P17" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="4">
@@ -2127,26 +2133,26 @@
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>144</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -2154,7 +2160,7 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
@@ -2175,53 +2181,53 @@
         <v>71</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>147</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>148</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="K19" s="9">
         <v>35617996.990000002</v>
       </c>
       <c r="L19" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="N19" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="O19" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="P19" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q19" s="4"/>
       <c r="R19" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="S19" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="T19" s="4"/>
       <c r="U19" s="4">

--- a/data/ERGA_ODIKA_UNIFIED.xlsx
+++ b/data/ERGA_ODIKA_UNIFIED.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mouhq-my.sharepoint.com/personal/ckourouklis_mou_gr/Documents/Qgis/1. Page combo Telika/roads_current/map-roads/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mouhq-my.sharepoint.com/personal/ckourouklis_mou_gr/Documents/Qgis/1. Page combo Telika/roads_odika_new_features/map-roads/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_A75A605B1059706FE76A745540DD1EB85657B408" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E05281A-01AB-409B-B241-7EB2F2C2D163}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_A75A605B1059706FE76A745540DD1EB85657B408" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB22D951-F167-4557-98AC-62142DD433B9}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="172">
   <si>
     <t>ΒΑΣΗ ΟΔΙΚΩΝ ΕΡΓΩΝ – ΕΔΥΜΕΤ</t>
   </si>
@@ -826,6 +826,12 @@
   </si>
   <si>
     <t xml:space="preserve">Α.Σ </t>
+  </si>
+  <si>
+    <t>6η Υδραυλικού Έργου</t>
+  </si>
+  <si>
+    <t>1ης ΣΣΕ</t>
   </si>
 </sst>
 </file>
@@ -1050,10 +1056,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1515,9 +1517,11 @@
         <v>160</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="T6" s="4"/>
+        <v>170</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>171</v>
+      </c>
       <c r="U6" s="4">
         <v>38.857239999999997</v>
       </c>
